--- a/backend/offer_module/veri/fiyat_listeleri/20260427_FIYAT_LISTESI_2026.xlsx
+++ b/backend/offer_module/veri/fiyat_listeleri/20260427_FIYAT_LISTESI_2026.xlsx
@@ -1306,7 +1306,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rainwater 40 LT Emaye Tank</t>
+          <t>Rainwater 80 LT Emaye Tank</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
